--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_917_Yemen_Arabian_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_917_Yemen_Arabian_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R678e68d595784ed3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rcc31a0554b9b4fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rcdab618540c54281"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R74015ff242e6488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4f9d03ec28654bd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R648aea92cacf4b91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb363e604745d4f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra2a09bc712884bb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R31c3c3b00fa64fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0d862c082e3e4607"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf629221cf21e4969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd41238c6c96a48e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ917CommercialTable" displayName="EEZ917CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ917CommercialTable" displayName="EEZ917CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ917FunctionalTable" displayName="EEZ917FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ917FunctionalTable" displayName="EEZ917FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ917ValidationTable" displayName="EEZ917ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ917ValidationTable" displayName="EEZ917ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3977,7 +3931,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab8408b11400455e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R697fd0d27b874f6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3987,20 +3941,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4008,552 +3952,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>974.5078743269</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.319077071466641</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>208.48608372005214</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>974.5078743269</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>208.86383086414153</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$50,A2,'Species'!$U$2:$U$50))</x:f>
-        <x:v>203539.44783918775</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.319077071466641</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>208.48608372005214</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>203171.33027276813</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>368.11756641961983</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.001811857834102</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.001811857834101902</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1193.3136939186</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.3448738055113605</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2212.451736243062</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1193.3136939186</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2370.51744185754</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$50,A3,'Species'!$U$2:$U$50))</x:f>
-        <x:v>2828770.9250414907</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.3448738055113605</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2212.451736243062</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2640148.9539928283</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>188621.97104866244</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0714436853130578</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.07144368531305784</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>27057.0441688626</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.41</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>25.703957827688647</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>27057.0441688626</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>25.703957827688644</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$50,A4,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>695473.1222583533</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.41</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>25.703957827688647</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>695473.1222583533</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>55.0446501412</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>55.0446501412</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$50,A5,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>692.9710884607609</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>692.9710884607609</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>139421.42453735528</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.277310888666368</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>189.36987332692482</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>139421.42453735528</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>203.01312537027536</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$50,A6,'Species'!$U$2:$U$50))</x:f>
-        <x:v>28304379.138904493</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.277310888666368</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>189.36987332692482</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>26402217.50369838</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1902161.6352061145</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0720455255298031</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.07204552552980305</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>53323.8879782216</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6754770322279877</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>473.6712572896261</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>53323.8879782216</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>828.5955192131876</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$50,A7,'Species'!$U$2:$U$50))</x:f>
-        <x:v>44183934.64578038</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6754770322279877</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>473.6712572896261</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>25257993.062215406</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>18925941.58356497</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7493050432370716</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7493050432370716</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>43.4271821272</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>43.4271821272</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$50,A8,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>34495.43691814863</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>34495.43691814863</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>16260.6428154717</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.170130584765365</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1479.5531970963605</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>16260.6428154717</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1511.3568581470863</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$50,A9,'Species'!$U$2:$U$50))</x:f>
-        <x:v>24575634.0370433</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.170130584765365</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1479.5531970963605</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>24058486.06447312</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>517147.9725701809</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0214954495135022</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.021495449513502313</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>86037.8597996627</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.427060527835576</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2673.3789728429856</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>86037.8597996627</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2683.108584945601</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$50,A10,'Species'!$U$2:$U$50))</x:f>
-        <x:v>230848920.25882098</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.427060527835576</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2673.3789728429856</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>230011805.25683108</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>837115.0019899011</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0036394436409695</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.003639443640969553</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0692c7c2f4704ad0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d8ae71236664be9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4563,20 +4148,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4584,930 +4159,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>9009.1577973367</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.601629176697249</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>399.6034018041084</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>9009.1577973367</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>400.00394094005605</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$50,A2,'Species'!$U$2:$U$50))</x:f>
-        <x:v>3603698.623485515</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.601629176697249</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>399.6034018041084</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3600090.1032057535</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3608.520279761404</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0010023416571014</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0010023416571013442</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1692.6327994500002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.406144354069477</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2547.676927902547</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1692.6327994500002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2567.7774662797287</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$50,A3,'Species'!$U$2:$U$50))</x:f>
-        <x:v>4346304.361113686</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.406144354069477</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2547.676927902547</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4312281.530569864</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>34022.83054382168</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0078897517016534</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.007889751701653298</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>91558.37185690881</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.430508008693904</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2694.685023768255</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>91558.37185690881</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2709.5718545355467</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$50,A4,'Species'!$U$2:$U$50))</x:f>
-        <x:v>248083987.4305796</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.430508008693904</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2694.685023768255</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>246720973.44341707</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1363013.9871625304</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0055245160885162</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.005524516088516178</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>43.4271821272</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>43.4271821272</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$50,A5,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>13732.88078849081</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>13732.88078849081</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>16260.6428154717</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.170130584765365</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1479.5531970963605</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>16260.6428154717</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1511.3568581470863</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$50,A6,'Species'!$U$2:$U$50))</x:f>
-        <x:v>24575634.0370433</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.170130584765365</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1479.5531970963605</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>24058486.06447312</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>517147.9725701809</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0214954495135022</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.021495449513502313</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>225.14797036750002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.349288284969354</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>223.50553617750256</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>225.14797036750002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>224.47367721730535</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$50,A7,'Species'!$U$2:$U$50))</x:f>
-        <x:v>50539.79282640563</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.349288284969354</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>223.50553617750256</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>50321.81783626455</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>217.97499014108325</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0043316199516148</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.004331619951614686</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>43.4271821272</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>2.93</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>85.11380382023768</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>43.4271821272</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>85.11380382023768</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$50,A8,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3696.2526600402325</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>2.93</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>85.11380382023768</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>3696.2526600402325</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>41604.319412040095</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4557614332167264</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>285.6021241890577</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>41604.319412040095</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>318.73527972742977</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$50,A9,'Species'!$U$2:$U$50))</x:f>
-        <x:v>13260764.385665936</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4557614332167264</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>285.6021241890577</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>11882281.999518698</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1378482.3861472383</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.116011586512008</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.11601158651200795</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>8479.1764798273</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.2954899494017145</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>197.46491808426984</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>8479.1764798273</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>340.1320652419234</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$50,A10,'Species'!$U$2:$U$50))</x:f>
-        <x:v>2884039.8076344016</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.2954899494017145</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>197.46491808426984</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1674339.8890111654</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1209699.9186232362</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.722493638575178</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.7224936385751778</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9926.1615446515</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.893213651552548</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>782.0124216732232</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9926.1615446515</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1076.443376616387</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$50,A11,'Species'!$U$2:$U$50))</x:f>
-        <x:v>10684950.849964393</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.893213651552548</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>782.0124216732232</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>7762381.627452542</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2922569.222511851</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.3765041919835344</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.3765041919835343</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>75.4797459139</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.0729263850516793</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>11.82841041636248</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>75.4797459139</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>11.88824942801661</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$50,A12,'Species'!$U$2:$U$50))</x:f>
-        <x:v>897.3220461877609</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.0729263850516793</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>11.82841041636248</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>892.8054127923682</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>4.51663339539266</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0050589225050353</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0050589225050353195</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>749.3599039594</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>749.3599039594</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$50,A13,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>152999.65501278214</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>152999.65501278214</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1433.2373802643</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.2272729739463677</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>168.76134343304471</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1433.2373802643</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>169.7420912993241</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$50,A14,'Species'!$U$2:$U$50))</x:f>
-        <x:v>243280.71025442693</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.2272729739463677</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>168.76134343304471</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>241875.06575186085</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1405.6445025660796</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0058114485600105</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.005811448560010429</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1717.0496871465</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.5113971098413193</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>324.63632237926373</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1717.0496871465</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>324.9323130478557</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$50,A15,'Species'!$U$2:$U$50))</x:f>
-        <x:v>557924.9264626092</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.5113971098413193</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>324.63632237926373</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>557416.695777705</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>508.2306849041488</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0009117607864169</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0009117607864168256</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>140356.2472485771</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0799975270043873</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>120.2257588603174</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>140356.2472485771</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>145.2348464903986</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$50,A16,'Species'!$U$2:$U$50))</x:f>
-        <x:v>20384618.023115527</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0799975270043873</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>120.2257588603174</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>16874436.336246517</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>3510181.6868690103</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2080177148986655</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.20801771489866555</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1193.3136939186</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>4.3448738055113605</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>2212.451736243062</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1193.3136939186</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>2370.51744185754</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$50,A17,'Species'!$U$2:$U$50))</x:f>
-        <x:v>2828770.9250414907</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>4.3448738055113605</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>2212.451736243062</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2640148.9539928283</x:v>
       </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>188621.97104866244</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0714436853130578</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.07144368531305784</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86038a49350f4c07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7be9cdd362cc4810"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5682,7 +4653,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5781,7 +4752,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>331675839.9836948</x:v>
+        <x:v>309304483.70174855</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5795,7 +4766,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>331675839.9836948</x:v>
+        <x:v>320546355.1211275</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5809,7 +4780,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-22371356.28194624</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5823,7 +4794,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-11129484.862567306</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5834,9 +4805,9 @@
         <x:v>EEZ_917</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5848,47 +4819,19 @@
         <x:v>EEZ_917</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_917</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_917</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0803f379a4a8423b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R655fdbe44bb44706"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5935,7 +4878,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
